--- a/Team-Data/2011-12/3-4-2011-12.xlsx
+++ b/Team-Data/2011-12/3-4-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
@@ -769,19 +836,19 @@
         <v>17</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>27</v>
       </c>
       <c r="AR2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS2" t="n">
         <v>12</v>
@@ -802,7 +869,7 @@
         <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -843,31 +910,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" t="n">
         <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>0.528</v>
+        <v>0.514</v>
       </c>
       <c r="H3" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="J3" t="n">
-        <v>76.5</v>
+        <v>75.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M3" t="n">
         <v>15.5</v>
@@ -876,64 +943,64 @@
         <v>0.372</v>
       </c>
       <c r="O3" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P3" t="n">
         <v>20.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R3" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="S3" t="n">
         <v>30.7</v>
       </c>
       <c r="T3" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.5</v>
       </c>
       <c r="W3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>90.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -954,7 +1021,7 @@
         <v>7</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -978,13 +1045,13 @@
         <v>22</v>
       </c>
       <c r="AW3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX3" t="n">
         <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -996,7 +1063,7 @@
         <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>0.114</v>
+        <v>0.118</v>
       </c>
       <c r="H4" t="n">
         <v>48.1</v>
@@ -1043,34 +1110,34 @@
         <v>33.4</v>
       </c>
       <c r="J4" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.413</v>
+        <v>0.414</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M4" t="n">
         <v>14.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.299</v>
+        <v>0.304</v>
       </c>
       <c r="O4" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="P4" t="n">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.737</v>
+        <v>0.725</v>
       </c>
       <c r="R4" t="n">
         <v>10.4</v>
       </c>
       <c r="S4" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T4" t="n">
         <v>39.9</v>
@@ -1079,31 +1146,31 @@
         <v>19.6</v>
       </c>
       <c r="V4" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X4" t="n">
         <v>5.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>86.7</v>
+        <v>86.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-14.5</v>
+        <v>-14.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1115,13 +1182,13 @@
         <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
@@ -1136,16 +1203,16 @@
         <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
         <v>26</v>
@@ -1157,7 +1224,7 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
         <v>30</v>
@@ -1166,13 +1233,13 @@
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>0.795</v>
+        <v>0.789</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
@@ -1237,22 +1304,22 @@
         <v>15.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="O5" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="R5" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S5" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T5" t="n">
         <v>45.6</v>
@@ -1264,7 +1331,7 @@
         <v>14</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
@@ -1282,7 +1349,7 @@
         <v>97.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1318,19 +1385,19 @@
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP5" t="n">
         <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR5" t="n">
         <v>2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
@@ -1342,7 +1409,7 @@
         <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1357,7 +1424,7 @@
         <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
         <v>23</v>
@@ -1479,7 +1546,7 @@
         <v>23</v>
       </c>
       <c r="AH6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI6" t="n">
         <v>24</v>
@@ -1506,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR6" t="n">
         <v>3</v>
@@ -1542,7 +1609,7 @@
         <v>22</v>
       </c>
       <c r="BC6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
@@ -1682,10 +1749,10 @@
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ7" t="n">
         <v>20</v>
@@ -1703,7 +1770,7 @@
         <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>3</v>
@@ -1712,16 +1779,16 @@
         <v>13</v>
       </c>
       <c r="AY7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
         <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
         <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.553</v>
+        <v>0.541</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J8" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.467</v>
+        <v>0.469</v>
       </c>
       <c r="L8" t="n">
         <v>6.7</v>
       </c>
       <c r="M8" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O8" t="n">
         <v>20.4</v>
@@ -1798,16 +1865,16 @@
         <v>11</v>
       </c>
       <c r="S8" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T8" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U8" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W8" t="n">
         <v>8.699999999999999</v>
@@ -1819,31 +1886,31 @@
         <v>6.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AA8" t="n">
         <v>23.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.7</v>
+        <v>103.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1855,7 +1922,7 @@
         <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="n">
         <v>6</v>
@@ -1864,19 +1931,19 @@
         <v>23</v>
       </c>
       <c r="AO8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP8" t="n">
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -1885,10 +1952,10 @@
         <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-6.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2022,16 +2089,16 @@
         <v>26</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
         <v>28</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
         <v>25</v>
@@ -2058,7 +2125,7 @@
         <v>7</v>
       </c>
       <c r="AS9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
         <v>26</v>
@@ -2079,10 +2146,10 @@
         <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -2117,82 +2184,82 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>0.412</v>
+        <v>0.424</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="J10" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L10" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="O10" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P10" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R10" t="n">
         <v>10.8</v>
       </c>
       <c r="S10" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T10" t="n">
         <v>40.1</v>
       </c>
       <c r="U10" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V10" t="n">
         <v>14.3</v>
       </c>
       <c r="W10" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y10" t="n">
         <v>4.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA10" t="n">
         <v>17.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>97</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AD10" t="n">
         <v>30</v>
@@ -2201,22 +2268,22 @@
         <v>21</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
         <v>9</v>
       </c>
       <c r="AK10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL10" t="n">
         <v>4</v>
@@ -2225,16 +2292,16 @@
         <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
         <v>26</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
         <v>20</v>
@@ -2246,7 +2313,7 @@
         <v>27</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2255,7 +2322,7 @@
         <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
         <v>2</v>
@@ -2267,10 +2334,10 @@
         <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -2299,43 +2366,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
         <v>21</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.553</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J11" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L11" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M11" t="n">
         <v>20.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.355</v>
+        <v>0.351</v>
       </c>
       <c r="O11" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P11" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0.788</v>
@@ -2353,7 +2420,7 @@
         <v>20.4</v>
       </c>
       <c r="V11" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W11" t="n">
         <v>7.5</v>
@@ -2365,31 +2432,31 @@
         <v>5.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA11" t="n">
         <v>18.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>97.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2398,7 +2465,7 @@
         <v>5</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2407,13 +2474,13 @@
         <v>9</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
@@ -2425,31 +2492,31 @@
         <v>19</v>
       </c>
       <c r="AT11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU11" t="n">
         <v>18</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
@@ -2583,19 +2650,19 @@
         <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM12" t="n">
         <v>21</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>6</v>
@@ -2604,7 +2671,7 @@
         <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
         <v>3</v>
@@ -2613,7 +2680,7 @@
         <v>27</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
         <v>9</v>
@@ -2634,7 +2701,7 @@
         <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -2663,37 +2730,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.629</v>
+        <v>0.618</v>
       </c>
       <c r="H13" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J13" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L13" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M13" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O13" t="n">
         <v>16.6</v>
@@ -2702,49 +2769,49 @@
         <v>23.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.695</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R13" t="n">
         <v>12</v>
       </c>
       <c r="S13" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="T13" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="U13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W13" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z13" t="n">
         <v>21.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>2.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AF13" t="n">
         <v>6</v>
@@ -2753,16 +2820,16 @@
         <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ13" t="n">
         <v>16</v>
       </c>
       <c r="AK13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL13" t="n">
         <v>5</v>
@@ -2780,13 +2847,13 @@
         <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
         <v>12</v>
@@ -2801,10 +2868,10 @@
         <v>15</v>
       </c>
       <c r="AX13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ13" t="n">
         <v>26</v>
@@ -2813,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
         <v>12</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.622</v>
+        <v>0.611</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,10 +2930,10 @@
         <v>35.9</v>
       </c>
       <c r="J14" t="n">
-        <v>79.2</v>
+        <v>79.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L14" t="n">
         <v>5.1</v>
@@ -2875,7 +2942,7 @@
         <v>16.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.303</v>
+        <v>0.304</v>
       </c>
       <c r="O14" t="n">
         <v>17.1</v>
@@ -2884,28 +2951,28 @@
         <v>22.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R14" t="n">
         <v>11.6</v>
       </c>
       <c r="S14" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T14" t="n">
         <v>45.8</v>
       </c>
       <c r="U14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V14" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
         <v>5.9</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
         <v>3.9</v>
@@ -2914,19 +2981,19 @@
         <v>18.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
@@ -2935,13 +3002,13 @@
         <v>8</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
         <v>16</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
         <v>7</v>
@@ -2956,7 +3023,7 @@
         <v>28</v>
       </c>
       <c r="AO14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP14" t="n">
         <v>13</v>
@@ -2977,13 +3044,13 @@
         <v>13</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW14" t="n">
         <v>29</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2992,13 +3059,13 @@
         <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB14" t="n">
         <v>20</v>
       </c>
       <c r="BC14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -3105,10 +3172,10 @@
         <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF15" t="n">
         <v>9</v>
@@ -3117,13 +3184,13 @@
         <v>9</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK15" t="n">
         <v>15</v>
@@ -3147,19 +3214,19 @@
         <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS15" t="n">
         <v>23</v>
       </c>
       <c r="AT15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
         <v>24</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
@@ -3171,7 +3238,7 @@
         <v>21</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -3209,61 +3276,61 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" t="n">
         <v>28</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.757</v>
+        <v>0.778</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="J16" t="n">
-        <v>79.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.484</v>
+        <v>0.488</v>
       </c>
       <c r="L16" t="n">
         <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.399</v>
+        <v>0.404</v>
       </c>
       <c r="O16" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="P16" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="R16" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="S16" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="T16" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U16" t="n">
         <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
         <v>8.6</v>
@@ -3272,28 +3339,28 @@
         <v>5.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>103.1</v>
+        <v>103.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
@@ -3320,37 +3387,37 @@
         <v>1</v>
       </c>
       <c r="AO16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AP16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
         <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AT16" t="n">
         <v>14</v>
       </c>
       <c r="AU16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX16" t="n">
         <v>14</v>
       </c>
-      <c r="AV16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>15</v>
-      </c>
       <c r="AY16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AZ16" t="n">
         <v>20</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
@@ -3481,7 +3548,7 @@
         <v>22</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
         <v>15</v>
@@ -3490,22 +3557,22 @@
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
         <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ17" t="n">
         <v>2</v>
@@ -3544,7 +3611,7 @@
         <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3718,25 @@
         <v>0.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
         <v>19</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK18" t="n">
         <v>22</v>
@@ -3684,7 +3751,7 @@
         <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP18" t="n">
         <v>3</v>
@@ -3708,7 +3775,7 @@
         <v>27</v>
       </c>
       <c r="AW18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX18" t="n">
         <v>27</v>
@@ -3717,13 +3784,13 @@
         <v>23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA18" t="n">
         <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.316</v>
+        <v>0.297</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3773,37 +3840,37 @@
         <v>33.6</v>
       </c>
       <c r="J19" t="n">
-        <v>79</v>
+        <v>79.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L19" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O19" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="P19" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="R19" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S19" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="T19" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U19" t="n">
         <v>19.8</v>
@@ -3815,46 +3882,46 @@
         <v>7.1</v>
       </c>
       <c r="X19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y19" t="n">
         <v>5.3</v>
       </c>
       <c r="Z19" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>20.2</v>
       </c>
-      <c r="AA19" t="n">
-        <v>20.4</v>
-      </c>
       <c r="AB19" t="n">
-        <v>92.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.4</v>
+        <v>-6.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF19" t="n">
         <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
       </c>
       <c r="AJ19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>2</v>
@@ -3863,22 +3930,22 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT19" t="n">
         <v>29</v>
@@ -3887,10 +3954,10 @@
         <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4072,7 +4139,7 @@
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX20" t="n">
         <v>21</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" t="n">
         <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="J21" t="n">
-        <v>80.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K21" t="n">
         <v>0.434</v>
@@ -4146,37 +4213,37 @@
         <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.308</v>
+        <v>0.305</v>
       </c>
       <c r="O21" t="n">
         <v>19.2</v>
       </c>
       <c r="P21" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="R21" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S21" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T21" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U21" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V21" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W21" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X21" t="n">
         <v>4.2</v>
@@ -4188,37 +4255,37 @@
         <v>21.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB21" t="n">
-        <v>96.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF21" t="n">
         <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
         <v>10</v>
@@ -4242,10 +4309,10 @@
         <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AU21" t="n">
         <v>23</v>
@@ -4260,7 +4327,7 @@
         <v>28</v>
       </c>
       <c r="AY21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ21" t="n">
         <v>24</v>
@@ -4272,7 +4339,7 @@
         <v>12</v>
       </c>
       <c r="BC21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>5.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,7 +4461,7 @@
         <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
         <v>28</v>
@@ -4406,7 +4473,7 @@
         <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN22" t="n">
         <v>14</v>
@@ -4445,7 +4512,7 @@
         <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA22" t="n">
         <v>11</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>2.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>5</v>
@@ -4573,10 +4640,10 @@
         <v>6</v>
       </c>
       <c r="AH23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
@@ -4594,10 +4661,10 @@
         <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4606,7 +4673,7 @@
         <v>17</v>
       </c>
       <c r="AS23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
         <v>8</v>
@@ -4618,13 +4685,13 @@
         <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX23" t="n">
         <v>26</v>
       </c>
       <c r="AY23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ23" t="n">
         <v>5</v>
@@ -4636,7 +4703,7 @@
         <v>19</v>
       </c>
       <c r="BC23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -4665,37 +4732,37 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
         <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>0.579</v>
+        <v>0.595</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J24" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="L24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M24" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.366</v>
+        <v>0.371</v>
       </c>
       <c r="O24" t="n">
         <v>13.4</v>
@@ -4704,22 +4771,22 @@
         <v>18.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.738</v>
+        <v>0.736</v>
       </c>
       <c r="R24" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="S24" t="n">
         <v>32.9</v>
       </c>
       <c r="T24" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U24" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V24" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="W24" t="n">
         <v>8.6</v>
@@ -4740,31 +4807,31 @@
         <v>94.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
         <v>5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4773,7 +4840,7 @@
         <v>24</v>
       </c>
       <c r="AN24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,7 +4852,7 @@
         <v>21</v>
       </c>
       <c r="AR24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS24" t="n">
         <v>3</v>
@@ -4794,16 +4861,16 @@
         <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY24" t="n">
         <v>8</v>
@@ -4815,7 +4882,7 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC24" t="n">
         <v>3</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F25" t="n">
         <v>20</v>
       </c>
       <c r="G25" t="n">
-        <v>0.459</v>
+        <v>0.444</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J25" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.447</v>
@@ -4874,40 +4941,40 @@
         <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="O25" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="P25" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.766</v>
+        <v>0.768</v>
       </c>
       <c r="R25" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S25" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T25" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="V25" t="n">
         <v>14.7</v>
       </c>
       <c r="W25" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y25" t="n">
         <v>4.4</v>
@@ -4916,22 +4983,22 @@
         <v>18.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB25" t="n">
         <v>94.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="n">
         <v>20</v>
@@ -4940,61 +5007,61 @@
         <v>29</v>
       </c>
       <c r="AI25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AK25" t="n">
         <v>14</v>
       </c>
       <c r="AL25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM25" t="n">
         <v>14</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>15</v>
       </c>
       <c r="AN25" t="n">
         <v>15</v>
       </c>
       <c r="AO25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ25" t="n">
         <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS25" t="n">
         <v>14</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW25" t="n">
         <v>24</v>
       </c>
       <c r="AX25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -5107,22 +5174,22 @@
         <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF26" t="n">
         <v>17</v>
       </c>
-      <c r="AF26" t="n">
-        <v>16</v>
-      </c>
       <c r="AG26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
         <v>6</v>
@@ -5134,7 +5201,7 @@
         <v>12</v>
       </c>
       <c r="AM26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
         <v>16</v>
@@ -5152,28 +5219,28 @@
         <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT26" t="n">
         <v>24</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
       </c>
       <c r="AW26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY26" t="n">
         <v>17</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
         <v>9</v>
@@ -5182,7 +5249,7 @@
         <v>5</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>0.324</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
@@ -5229,25 +5296,25 @@
         <v>35.2</v>
       </c>
       <c r="J27" t="n">
-        <v>85.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.413</v>
       </c>
       <c r="L27" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M27" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.312</v>
+        <v>0.314</v>
       </c>
       <c r="O27" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P27" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="Q27" t="n">
         <v>0.751</v>
@@ -5256,19 +5323,19 @@
         <v>14</v>
       </c>
       <c r="S27" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T27" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U27" t="n">
         <v>17.5</v>
       </c>
       <c r="V27" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X27" t="n">
         <v>4.5</v>
@@ -5277,19 +5344,19 @@
         <v>6.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC27" t="n">
         <v>-7.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>20</v>
@@ -5316,7 +5383,7 @@
         <v>17</v>
       </c>
       <c r="AM27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AN27" t="n">
         <v>26</v>
@@ -5325,16 +5392,16 @@
         <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
         <v>5</v>
@@ -5343,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
@@ -5355,7 +5422,7 @@
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -5393,55 +5460,55 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E28" t="n">
         <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.676</v>
+        <v>0.694</v>
       </c>
       <c r="H28" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="J28" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="O28" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P28" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0.728</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T28" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U28" t="n">
         <v>22.2</v>
@@ -5453,25 +5520,25 @@
         <v>7.1</v>
       </c>
       <c r="X28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y28" t="n">
         <v>5.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5483,13 +5550,13 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI28" t="n">
         <v>4</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
@@ -5504,7 +5571,7 @@
         <v>2</v>
       </c>
       <c r="AO28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP28" t="n">
         <v>19</v>
@@ -5513,22 +5580,22 @@
         <v>24</v>
       </c>
       <c r="AR28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX28" t="n">
         <v>25</v>
@@ -5546,7 +5613,7 @@
         <v>4</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -5575,55 +5642,55 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
         <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.324</v>
+        <v>0.306</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="J29" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.433</v>
+        <v>0.435</v>
       </c>
       <c r="L29" t="n">
         <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O29" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P29" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.755</v>
+        <v>0.751</v>
       </c>
       <c r="R29" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S29" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T29" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
@@ -5641,40 +5708,40 @@
         <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>89.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ29" t="n">
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
         <v>23</v>
@@ -5683,28 +5750,28 @@
         <v>19</v>
       </c>
       <c r="AN29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ29" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS29" t="n">
         <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV29" t="n">
         <v>21</v>
@@ -5716,19 +5783,19 @@
         <v>16</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB29" t="n">
         <v>27</v>
       </c>
       <c r="BC29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -5835,28 +5902,28 @@
         <v>-1.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
         <v>19</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
         <v>19</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL30" t="n">
         <v>29</v>
@@ -5895,10 +5962,10 @@
         <v>10</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6035,7 +6102,7 @@
         <v>14</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK31" t="n">
         <v>23</v>
@@ -6050,22 +6117,22 @@
         <v>24</v>
       </c>
       <c r="AO31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-4-2011-12</t>
+          <t>2012-03-04</t>
         </is>
       </c>
     </row>
